--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46079.66320601852</v>
+        <v>46081.58387731481</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46080.57303240741</v>
+        <v>46083.40001157407</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46022.31462962963</v>
+        <v>46081.48543981482</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>46080.37438657408</v>
+        <v>46083.38950231481</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>46072.69914351852</v>
+        <v>46080.81806712963</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="F131" s="3" t="n">
-        <v>46072.28550925926</v>
+        <v>46083.32769675926</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="F132" s="3" t="n">
-        <v>46071.32797453704</v>
+        <v>46083.32954861111</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="F133" s="3" t="n">
-        <v>46062.39050925926</v>
+        <v>46083.36475694444</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="F153" s="3" t="n">
-        <v>46077.36754629629</v>
+        <v>46083.32688657408</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="F161" s="3" t="n">
-        <v>46074.58900462963</v>
+        <v>46083.3734375</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="F180" s="3" t="n">
-        <v>46079.66320601852</v>
+        <v>46081.58387731481</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="F203" s="3" t="n">
-        <v>46080.37048611111</v>
+        <v>46081.60982638889</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         </is>
       </c>
       <c r="F262" s="3" t="n">
-        <v>46080.57782407408</v>
+        <v>46083.33503472222</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="F290" s="3" t="n">
-        <v>45904.46747685185</v>
+        <v>46081.58871527778</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="F291" s="3" t="n">
-        <v>46056.61079861111</v>
+        <v>46081.3878125</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="F297" s="3" t="n">
-        <v>45869.52688657407</v>
+        <v>46083.34431712963</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="F326" s="3" t="n">
-        <v>46073.65109953703</v>
+        <v>46081.45009259259</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46083.40001157407</v>
+        <v>46083.47232638889</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>46079.52180555555</v>
+        <v>46083.42251157408</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46078.38149305555</v>
+        <v>46083.4137962963</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46083.47232638889</v>
+        <v>46083.56194444445</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ASS_DIR02</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>PA_145</t>
+          <t>PA_130</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="F154" s="3" t="n">
-        <v>46080.69226851852</v>
+        <v>46083.56508101852</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -6043,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="F329" s="3" t="n">
-        <v>46060.41546296296</v>
+        <v>46083.50671296296</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PA_142</t>
+          <t>PA_146</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46083.56194444445</v>
+        <v>46083.6396875</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="F180" s="3" t="n">
-        <v>46081.58387731481</v>
+        <v>46083.62560185185</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="F197" s="3" t="n">
-        <v>46036.77550925926</v>
+        <v>46083.63334490741</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46083.4137962963</v>
+        <v>46083.6218287037</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="F272" s="3" t="n">
-        <v>46036.80780092593</v>
+        <v>46083.58152777778</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>PA_144</t>
+          <t>PA_137</t>
         </is>
       </c>
     </row>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46083.6396875</v>
+        <v>46083.72195601852</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>46073.45769675926</v>
+        <v>46083.69092592593</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4537,11 +4537,6 @@
       <c r="F126" s="3" t="n">
         <v>46055.31995370371</v>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>PA_034</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9635,7 +9630,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>PA_143</t>
+          <t>PA_147</t>
         </is>
       </c>
     </row>
@@ -9857,7 +9852,7 @@
         </is>
       </c>
       <c r="F290" s="3" t="n">
-        <v>46081.58871527778</v>
+        <v>46083.70072916667</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -965,11 +965,6 @@
       <c r="F17" s="3" t="n">
         <v>46083.72195601852</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PA_043</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1778,7 +1773,7 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>46083.69092592593</v>
+        <v>46084.31946759259</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4438,11 +4433,6 @@
       <c r="F123" s="3" t="n">
         <v>46071.53287037037</v>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>PA_038</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4895,11 +4885,6 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>PA_033</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5906,7 +5891,7 @@
         </is>
       </c>
       <c r="F168" s="3" t="n">
-        <v>46077.45071759259</v>
+        <v>46084.2702199074</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -7051,7 +7036,7 @@
         </is>
       </c>
       <c r="F203" s="3" t="n">
-        <v>46081.60982638889</v>
+        <v>46083.9482175926</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -8773,7 +8758,7 @@
         </is>
       </c>
       <c r="F257" s="3" t="n">
-        <v>46077.45071759259</v>
+        <v>46084.2702199074</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -9626,12 +9611,7 @@
         </is>
       </c>
       <c r="F283" s="3" t="n">
-        <v>45992.58188657407</v>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>PA_147</t>
-        </is>
+        <v>46084.31946759259</v>
       </c>
     </row>
     <row r="284">

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,12 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46083.72195601852</v>
+        <v>46084.40417824074</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PA_041</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -2598,7 +2603,7 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>46078.61869212963</v>
+        <v>46084.34930555556</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4433,6 +4438,11 @@
       <c r="F123" s="3" t="n">
         <v>46071.53287037037</v>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>PA_038</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4527,6 +4537,11 @@
       <c r="F126" s="3" t="n">
         <v>46055.31995370371</v>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PA_034</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4885,6 +4900,11 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PA_033</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6023,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6056,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6335,7 @@
         </is>
       </c>
       <c r="F181" s="3" t="n">
-        <v>46079.38373842592</v>
+        <v>46084.34077546297</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -2306,11 +2306,11 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>46064.6058912037</v>
+        <v>46084.43568287037</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PA_244</t>
+          <t>PA_149</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>46064.41614583333</v>
+        <v>46084.47333333334</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="F153" s="3" t="n">
-        <v>46083.32688657408</v>
+        <v>46084.43568287037</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="F166" s="3" t="n">
-        <v>46078.56081018518</v>
+        <v>46084.46637731481</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -6043,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="F190" s="3" t="n">
-        <v>46064.41614583333</v>
+        <v>46084.47333333334</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -6799,6 +6799,11 @@
       <c r="F195" s="3" t="n">
         <v>46066.34356481482</v>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>ASS_DIR02</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9598,7 +9603,7 @@
         </is>
       </c>
       <c r="F282" s="3" t="n">
-        <v>46078.56081018518</v>
+        <v>46084.46637731481</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>46076.42503472222</v>
+        <v>46084.5037037037</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>46072.39902777778</v>
+        <v>46084.49026620371</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="F161" s="3" t="n">
-        <v>46083.3734375</v>
+        <v>46084.5146875</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -6043,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
         </is>
       </c>
       <c r="F292" s="3" t="n">
-        <v>46077.51076388889</v>
+        <v>46084.55180555556</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>46062.3052662037</v>
+        <v>46084.58770833333</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46083.6218287037</v>
+        <v>46084.58667824074</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -10332,12 +10332,7 @@
         </is>
       </c>
       <c r="F305" s="3" t="n">
-        <v>46015.3359837963</v>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>PA_137</t>
-        </is>
+        <v>46084.58667824074</v>
       </c>
     </row>
     <row r="306">

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>46042.59778935185</v>
+        <v>46084.71726851852</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -6043,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="F291" s="3" t="n">
-        <v>46081.3878125</v>
+        <v>46084.70274305555</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>46058.36474537037</v>
+        <v>46084.7759375</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4537,11 +4537,6 @@
       <c r="F126" s="3" t="n">
         <v>46055.31995370371</v>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>PA_034</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4900,11 +4895,6 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>PA_033</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6043,11 +6033,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6066,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8468,7 @@
         </is>
       </c>
       <c r="F247" s="3" t="n">
-        <v>46080.4740625</v>
+        <v>46084.79648148148</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -9278,7 +9268,7 @@
         </is>
       </c>
       <c r="F272" s="3" t="n">
-        <v>46083.58152777778</v>
+        <v>46084.82578703704</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -10271,7 +10261,12 @@
         </is>
       </c>
       <c r="F303" s="3" t="n">
-        <v>46064.65435185185</v>
+        <v>46084.96498842593</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>AUDITORIO_14</t>
+        </is>
       </c>
     </row>
     <row r="304">

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46084.40417824074</v>
+        <v>46085.37086805556</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PA_041</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -4537,6 +4537,11 @@
       <c r="F126" s="3" t="n">
         <v>46055.31995370371</v>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PA_034</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4895,6 +4900,11 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PA_033</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8468,7 +8478,7 @@
         </is>
       </c>
       <c r="F247" s="3" t="n">
-        <v>46084.79648148148</v>
+        <v>46085.34269675926</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46085.37086805556</v>
+        <v>46085.48634259259</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philips TV</t>
+          <t>PHILIPS</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1029,11 +1029,11 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46080.41133101852</v>
+        <v>46085.44678240741</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>saladereuniao</t>
+          <t>Cesar-Estilo</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>46084.71726851852</v>
+        <v>46085.48582175926</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -6043,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="F281" s="3" t="n">
-        <v>46072.81847222222</v>
+        <v>46085.45099537037</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>AUDITORIO_14</t>
+          <t>RH05NEW</t>
         </is>
       </c>
     </row>
@@ -10338,6 +10338,11 @@
       </c>
       <c r="F305" s="3" t="n">
         <v>46084.58667824074</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>PA_144</t>
+        </is>
       </c>
     </row>
     <row r="306">

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46085.48634259259</v>
+        <v>46085.56425925926</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>46084.5037037037</v>
+        <v>46085.53319444445</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46085.56425925926</v>
+        <v>46085.60581018519</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PHILIPS</t>
+          <t>Philips TV</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1029,11 +1029,11 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46085.44678240741</v>
+        <v>46085.57503472222</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cesar-Estilo</t>
+          <t>saladereuniao</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>46084.34930555556</v>
+        <v>46085.58146990741</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -6043,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="F301" s="3" t="n">
-        <v>46076.65614583333</v>
+        <v>46085.70221064815</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -965,11 +965,6 @@
       <c r="F17" s="3" t="n">
         <v>46085.60581018519</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PA_043</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2042,7 +2037,7 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>46074.37412037037</v>
+        <v>46085.94978009259</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2730,7 +2725,7 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>46041.7121412037</v>
+        <v>46085.82708333333</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4438,11 +4433,6 @@
       <c r="F123" s="3" t="n">
         <v>46071.53287037037</v>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>PA_038</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4537,11 +4527,6 @@
       <c r="F126" s="3" t="n">
         <v>46055.31995370371</v>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>PA_034</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6043,11 +6028,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6061,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -8696,6 +8681,11 @@
       <c r="F254" s="3" t="n">
         <v>45869.62259259259</v>
       </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>PA_230</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10337,7 +10327,7 @@
         </is>
       </c>
       <c r="F305" s="3" t="n">
-        <v>46084.58667824074</v>
+        <v>46085.86240740741</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,12 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46085.60581018519</v>
+        <v>46086.36613425926</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PA_041</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -2598,7 +2603,7 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>46085.58146990741</v>
+        <v>46086.39978009259</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3083,11 +3088,11 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>45987.72282407407</v>
+        <v>46086.33987268519</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>BALEIA_C07</t>
+          <t>LAUREANO_C01</t>
         </is>
       </c>
     </row>
@@ -3182,11 +3187,11 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>46059.59628472223</v>
+        <v>46086.33871527778</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>LAUREANO_C01</t>
+          <t>BALEIA_C07</t>
         </is>
       </c>
     </row>
@@ -4433,6 +4438,11 @@
       <c r="F123" s="3" t="n">
         <v>46071.53287037037</v>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>PA_038</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4527,6 +4537,11 @@
       <c r="F126" s="3" t="n">
         <v>46055.31995370371</v>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PA_034</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6028,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6061,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46086.36613425926</v>
+        <v>46086.47979166666</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>46085.48582175926</v>
+        <v>46086.43935185186</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -10276,11 +10276,11 @@
         </is>
       </c>
       <c r="F303" s="3" t="n">
-        <v>46084.96498842593</v>
+        <v>46086.44290509259</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>RH05NEW</t>
+          <t>RH05</t>
         </is>
       </c>
     </row>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46086.47979166666</v>
+        <v>46086.56407407407</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PA_041</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>46086.43935185186</v>
+        <v>46086.49575231481</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>46086.49575231481</v>
+        <v>46086.58530092592</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="F303" s="3" t="n">
-        <v>46086.44290509259</v>
+        <v>46086.58530092592</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -965,11 +965,6 @@
       <c r="F17" s="3" t="n">
         <v>46086.56407407407</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PA_043</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1910,7 +1905,7 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>46084.7759375</v>
+        <v>46086.75908564815</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4438,11 +4433,6 @@
       <c r="F123" s="3" t="n">
         <v>46071.53287037037</v>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>PA_038</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4900,11 +4890,6 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>PA_033</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6043,11 +6028,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6061,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7013,7 @@
         </is>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46084.58667824074</v>
+        <v>46086.70513888889</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -8695,11 +8680,6 @@
       </c>
       <c r="F254" s="3" t="n">
         <v>45869.62259259259</v>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>PA_230</t>
-        </is>
       </c>
     </row>
     <row r="255">

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -965,6 +965,11 @@
       <c r="F17" s="3" t="n">
         <v>46086.56407407407</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PA_043</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4367,11 +4372,6 @@
       <c r="F121" s="3" t="n">
         <v>46034.35</v>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>PA_036</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4433,6 +4433,11 @@
       <c r="F123" s="3" t="n">
         <v>46071.53287037037</v>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>PA_038</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4890,6 +4895,11 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PA_033</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5896,7 +5906,7 @@
         </is>
       </c>
       <c r="F168" s="3" t="n">
-        <v>46084.2702199074</v>
+        <v>46087.34012731481</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -6028,11 +6038,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6061,11 +6071,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -8112,11 +8122,6 @@
       <c r="F236" s="3" t="n">
         <v>46036.62107638889</v>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>PA_031</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8768,7 +8773,7 @@
         </is>
       </c>
       <c r="F257" s="3" t="n">
-        <v>46084.2702199074</v>
+        <v>46087.34012731481</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -4372,6 +4372,11 @@
       <c r="F121" s="3" t="n">
         <v>46034.35</v>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>PA_036</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>46085.82708333333</v>
+        <v>46087.5547337963</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4900,11 +4900,6 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>PA_033</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5449,7 +5444,7 @@
         </is>
       </c>
       <c r="F154" s="3" t="n">
-        <v>46083.56508101852</v>
+        <v>46087.52108796296</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -6043,11 +6038,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6071,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46086.56407407407</v>
+        <v>46087.60232638889</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>46086.39978009259</v>
+        <v>46087.64291666666</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4900,6 +4900,11 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PA_033</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8468,7 +8473,7 @@
         </is>
       </c>
       <c r="F247" s="3" t="n">
-        <v>46085.34269675926</v>
+        <v>46087.59486111111</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46087.60232638889</v>
+        <v>46087.72540509259</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46087.72540509259</v>
+        <v>46088.44432870371</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>45868.74604166667</v>
+        <v>46088.43711805555</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>46084.49026620371</v>
+        <v>46088.45923611111</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4370,12 +4370,7 @@
         </is>
       </c>
       <c r="F121" s="3" t="n">
-        <v>46034.35</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>PA_036</t>
-        </is>
+        <v>46088.39179398148</v>
       </c>
     </row>
     <row r="122">
@@ -4403,7 +4398,7 @@
         </is>
       </c>
       <c r="F122" s="3" t="n">
-        <v>46071.37371527778</v>
+        <v>46088.40112268519</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4436,7 +4431,7 @@
         </is>
       </c>
       <c r="F123" s="3" t="n">
-        <v>46071.53287037037</v>
+        <v>46090.29378472222</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4469,7 +4464,7 @@
         </is>
       </c>
       <c r="F124" s="3" t="n">
-        <v>46072.37743055556</v>
+        <v>46088.51344907407</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4535,12 +4530,7 @@
         </is>
       </c>
       <c r="F126" s="3" t="n">
-        <v>46055.31995370371</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>PA_034</t>
-        </is>
+        <v>46088.38275462963</v>
       </c>
     </row>
     <row r="127">
@@ -4568,7 +4558,7 @@
         </is>
       </c>
       <c r="F127" s="3" t="n">
-        <v>46071.37371527778</v>
+        <v>46088.40112268519</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4601,7 +4591,7 @@
         </is>
       </c>
       <c r="F128" s="3" t="n">
-        <v>46071.53287037037</v>
+        <v>46088.43267361111</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4667,12 +4657,7 @@
         </is>
       </c>
       <c r="F130" s="3" t="n">
-        <v>46072.54927083333</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>PA_035</t>
-        </is>
+        <v>46088.42204861111</v>
       </c>
     </row>
     <row r="131">
@@ -4700,7 +4685,7 @@
         </is>
       </c>
       <c r="F131" s="3" t="n">
-        <v>46083.32769675926</v>
+        <v>46088.42802083334</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4733,7 +4718,7 @@
         </is>
       </c>
       <c r="F132" s="3" t="n">
-        <v>46083.32954861111</v>
+        <v>46088.38275462963</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4766,7 +4751,7 @@
         </is>
       </c>
       <c r="F133" s="3" t="n">
-        <v>46083.36475694444</v>
+        <v>46088.39179398148</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4799,7 +4784,7 @@
         </is>
       </c>
       <c r="F134" s="3" t="n">
-        <v>46072.54927083333</v>
+        <v>46088.42204861111</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4865,12 +4850,7 @@
         </is>
       </c>
       <c r="F136" s="3" t="n">
-        <v>46072.37743055556</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>PA_037</t>
-        </is>
+        <v>46088.51344907407</v>
       </c>
     </row>
     <row r="137">
@@ -4900,11 +4880,6 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>PA_033</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6142,7 +6117,7 @@
         </is>
       </c>
       <c r="F175" s="3" t="n">
-        <v>45868.74604166667</v>
+        <v>46088.43711805555</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -7028,7 +7003,7 @@
         </is>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46086.70513888889</v>
+        <v>46088.60243055555</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -8691,6 +8666,11 @@
       <c r="F254" s="3" t="n">
         <v>45869.62259259259</v>
       </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>PA_230</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10365,7 +10345,7 @@
         </is>
       </c>
       <c r="F306" s="3" t="n">
-        <v>46079.46703703704</v>
+        <v>46088.44050925926</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46088.44432870371</v>
+        <v>46090.38180555555</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>46088.43711805555</v>
+        <v>46090.32666666667</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>46055.61493055556</v>
+        <v>46090.39174768519</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PA_204</t>
+          <t>PA_244</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="F122" s="3" t="n">
-        <v>46088.40112268519</v>
+        <v>46090.37094907407</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="F127" s="3" t="n">
-        <v>46088.40112268519</v>
+        <v>46090.37094907407</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="F131" s="3" t="n">
-        <v>46088.42802083334</v>
+        <v>46090.32371527778</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4852,6 +4852,11 @@
       <c r="F136" s="3" t="n">
         <v>46088.51344907407</v>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>PA_037</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4880,6 +4885,11 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PA_033</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6018,11 +6028,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6051,11 +6061,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6127,7 @@
         </is>
       </c>
       <c r="F175" s="3" t="n">
-        <v>46088.43711805555</v>
+        <v>46090.32666666667</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -8448,7 +8458,7 @@
         </is>
       </c>
       <c r="F247" s="3" t="n">
-        <v>46087.59486111111</v>
+        <v>46090.33364583334</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46090.38180555555</v>
+        <v>46090.48094907407</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_041</t>
         </is>
       </c>
     </row>
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>46090.39174768519</v>
+        <v>46090.45797453704</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PA_244</t>
+          <t>PA_204</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,12 @@
         </is>
       </c>
       <c r="F121" s="3" t="n">
-        <v>46088.39179398148</v>
+        <v>46090.41075231481</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>PA_036</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -4659,6 +4664,11 @@
       <c r="F130" s="3" t="n">
         <v>46088.42204861111</v>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>PA_035</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4751,7 +4761,7 @@
         </is>
       </c>
       <c r="F133" s="3" t="n">
-        <v>46088.39179398148</v>
+        <v>46090.41075231481</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -5368,7 +5378,7 @@
         </is>
       </c>
       <c r="F152" s="3" t="n">
-        <v>46080.55364583333</v>
+        <v>46090.46891203704</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -6028,11 +6038,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6061,11 +6071,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6330,7 @@
         </is>
       </c>
       <c r="F181" s="3" t="n">
-        <v>46084.34077546297</v>
+        <v>46090.41965277777</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46090.48094907407</v>
+        <v>46090.57019675926</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PA_041</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -2438,11 +2438,11 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>45915.46722222222</v>
+        <v>46090.49665509259</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t>PA_257</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,12 @@
         </is>
       </c>
       <c r="F126" s="3" t="n">
-        <v>46088.38275462963</v>
+        <v>46090.56420138889</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PA_034</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -4728,7 +4733,7 @@
         </is>
       </c>
       <c r="F132" s="3" t="n">
-        <v>46088.38275462963</v>
+        <v>46090.56420138889</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -5444,7 +5449,7 @@
         </is>
       </c>
       <c r="F154" s="3" t="n">
-        <v>46087.52108796296</v>
+        <v>46090.5240625</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -6038,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6071,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -8122,6 +8127,11 @@
       <c r="F236" s="3" t="n">
         <v>46036.62107638889</v>
       </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>PA_031</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9178,7 +9188,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>PA_238</t>
+          <t>PA_256</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9283,7 @@
         </is>
       </c>
       <c r="F272" s="3" t="n">
-        <v>46084.82578703704</v>
+        <v>46090.49344907407</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>46079.63311342592</v>
+        <v>46090.63077546296</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="F168" s="3" t="n">
-        <v>46087.34012731481</v>
+        <v>46090.64215277778</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="F257" s="3" t="n">
-        <v>46087.34012731481</v>
+        <v>46090.64215277778</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="F264" s="3" t="n">
-        <v>46079.63311342592</v>
+        <v>46090.63077546296</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="F268" s="3" t="n">
-        <v>46065.61431712963</v>
+        <v>46090.63333333333</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="F123" s="3" t="n">
-        <v>46090.29378472222</v>
+        <v>46090.68164351852</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="F128" s="3" t="n">
-        <v>46088.43267361111</v>
+        <v>46090.68164351852</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -965,11 +965,6 @@
       <c r="F17" s="3" t="n">
         <v>46090.57019675926</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PA_043</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4899,11 +4894,6 @@
       </c>
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>PA_033</t>
-        </is>
       </c>
     </row>
     <row r="138">

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -965,6 +965,11 @@
       <c r="F17" s="3" t="n">
         <v>46090.57019675926</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PA_043</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4367,11 +4372,6 @@
       <c r="F121" s="3" t="n">
         <v>46090.41075231481</v>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>PA_036</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="F124" s="3" t="n">
-        <v>46088.51344907407</v>
+        <v>46091.36462962963</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>46046.38410879629</v>
+        <v>46091.35789351852</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="F136" s="3" t="n">
-        <v>46088.51344907407</v>
+        <v>46091.36462962963</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4895,6 +4895,11 @@
       <c r="F137" s="3" t="n">
         <v>46072.28550925926</v>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PA_033</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5901,7 +5906,7 @@
         </is>
       </c>
       <c r="F168" s="3" t="n">
-        <v>46090.64215277778</v>
+        <v>46091.33829861111</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -8115,12 +8120,7 @@
         </is>
       </c>
       <c r="F236" s="3" t="n">
-        <v>46036.62107638889</v>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>PA_031</t>
-        </is>
+        <v>46091.35789351852</v>
       </c>
     </row>
     <row r="237">
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="F247" s="3" t="n">
-        <v>46090.33364583334</v>
+        <v>46091.34012731481</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="F257" s="3" t="n">
-        <v>46090.64215277778</v>
+        <v>46091.33829861111</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="F279" s="3" t="n">
-        <v>46064.45865740741</v>
+        <v>46091.38575231482</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>45895.44690972222</v>
+        <v>46091.48170138889</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4372,6 +4372,11 @@
       <c r="F121" s="3" t="n">
         <v>46090.41075231481</v>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>PA_036</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4662,7 +4667,7 @@
         </is>
       </c>
       <c r="F130" s="3" t="n">
-        <v>46088.42204861111</v>
+        <v>46091.4471412037</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4794,7 +4799,7 @@
         </is>
       </c>
       <c r="F134" s="3" t="n">
-        <v>46088.42204861111</v>
+        <v>46091.4471412037</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -6038,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6071,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7716,7 @@
         </is>
       </c>
       <c r="F223" s="3" t="n">
-        <v>46066.49469907407</v>
+        <v>46091.43186342593</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46090.57019675926</v>
+        <v>46091.56130787037</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_234</t>
         </is>
       </c>
     </row>
@@ -4537,11 +4537,6 @@
       <c r="F126" s="3" t="n">
         <v>46090.56420138889</v>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>PA_034</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4832,7 +4827,7 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>46091.35789351852</v>
+        <v>46091.56011574074</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -9923,7 +9918,7 @@
         </is>
       </c>
       <c r="F292" s="3" t="n">
-        <v>46084.55180555556</v>
+        <v>46091.56655092593</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46091.56130787037</v>
+        <v>46091.58100694444</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PA_234</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -3651,11 +3651,6 @@
       <c r="F99" s="3" t="n">
         <v>46042.48149305556</v>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>PA_240</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4536,6 +4531,11 @@
       </c>
       <c r="F126" s="3" t="n">
         <v>46090.56420138889</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PA_034</t>
+        </is>
       </c>
     </row>
     <row r="127">

--- a/Monitores.xlsx
+++ b/Monitores.xlsx
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>45890.44893518519</v>
+        <v>46091.70070601852</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3651,6 +3651,11 @@
       <c r="F99" s="3" t="n">
         <v>46042.48149305556</v>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>PA_240</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3875,7 +3880,7 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>45891.38046296296</v>
+        <v>46091.69876157407</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6038,11 +6043,11 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>46055.83954861111</v>
+        <v>46064.43611111111</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>PA_054</t>
+          <t>PA_043</t>
         </is>
       </c>
     </row>
@@ -6071,11 +6076,11 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>46064.43611111111</v>
+        <v>46055.83954861111</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>PA_043</t>
+          <t>PA_054</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6797,7 @@
         </is>
       </c>
       <c r="F195" s="3" t="n">
-        <v>46066.34356481482</v>
+        <v>46091.67689814815</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -9075,7 +9080,7 @@
         </is>
       </c>
       <c r="F266" s="3" t="n">
-        <v>45890.44893518519</v>
+        <v>46091.70070601852</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -11119,7 +11124,7 @@
         </is>
       </c>
       <c r="F329" s="3" t="n">
-        <v>46083.50671296296</v>
+        <v>46091.69876157407</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
